--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.171.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.171.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.171" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.171" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.171.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.171.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0171.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0171.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.171.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.171.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.171" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.171" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: MASTERâ€™S OFFICEâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]164</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]164</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 164</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L8: isolated marker/symbol line :: s</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]164</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L141: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L141: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 103â€”104</t>
+          <t>L140: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L11: isolated marker/symbol line :: E</t>
+          <t>L8: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -732,7 +736,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 86â€”87</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -744,7 +748,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L13: isolated marker/symbol line :: S</t>
+          <t>L11: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -789,11 +793,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L14: isolated marker/symbol line :: C</t>
+          <t>L13: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -848,11 +848,7 @@
       </c>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -862,7 +858,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L16: isolated marker/symbol line :: V</t>
+          <t>L14: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -917,7 +913,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 94</t>
+          <t>L16: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -964,7 +960,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 94</t>
+          <t>L46: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1011,7 +1007,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 0</t>
+          <t>L48: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1038,7 +1034,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1058,7 +1054,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 146</t>
+          <t>L54: symbol-only separator/garbage line :: 103—104</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1085,7 +1081,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L62: symbol-only separator/garbage line :: . 142</t>
+          <t>L56: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1132,7 +1128,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1152,7 +1148,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: P</t>
+          <t>L60: isolated marker/symbol line :: 146</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1199,7 +1195,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: C</t>
+          <t>L62: symbol-only separator/garbage line :: . 142</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1246,7 +1242,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: I</t>
+          <t>L64: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1293,7 +1289,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: E</t>
+          <t>L67: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1340,7 +1336,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: T</t>
+          <t>L69: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1387,7 +1383,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: v</t>
+          <t>L70: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1422,7 +1418,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 0</t>
+          <t>L72: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1457,7 +1453,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 0</t>
+          <t>L73: isolated marker/symbol line :: v</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1492,7 +1488,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: R</t>
+          <t>L76: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1522,12 +1518,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: C</t>
+          <t>L78: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1562,7 +1558,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: N</t>
+          <t>L82: isolated marker/symbol line :: R</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1597,7 +1593,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: E</t>
+          <t>L84: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1632,7 +1628,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 0</t>
+          <t>L88: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1667,7 +1663,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 0</t>
+          <t>L90: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1702,7 +1698,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 114</t>
+          <t>L91: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1737,7 +1733,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 110</t>
+          <t>L94: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1772,7 +1768,7 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: ,</t>
+          <t>L96: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1807,7 +1803,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L122: symbol-only separator/garbage line :: .155</t>
+          <t>L116: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1842,7 +1838,7 @@
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: . 105</t>
+          <t>L118: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1877,7 +1873,7 @@
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 116</t>
+          <t>L120: symbol-only separator/garbage line :: . 86—87</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1912,7 +1908,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L122: symbol-only separator/garbage line :: .155</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1947,7 +1943,7 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 1</t>
+          <t>L124: symbol-only separator/garbage line :: . 105</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -1982,7 +1978,7 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: 1</t>
+          <t>L125: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2017,7 +2013,7 @@
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 1</t>
+          <t>L140: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2052,7 +2048,7 @@
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L142: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: .2</t>
+          <t>L144: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2122,7 +2118,7 @@
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: C</t>
+          <t>L146: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2157,7 +2153,7 @@
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L158: isolated marker/symbol line | line starts with punctuation glued to text :: .E</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2190,7 +2186,11 @@
           <t>L99: isolated marker/symbol line :: ,</t>
         </is>
       </c>
-      <c r="O40" s="1" t="inlineStr"/>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L150: isolated marker/symbol line :: .2</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2221,7 +2221,11 @@
           <t>L100: isolated marker/symbol line :: 110</t>
         </is>
       </c>
-      <c r="O41" s="1" t="inlineStr"/>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L157: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2252,7 +2256,11 @@
           <t>L101: isolated marker/symbol line :: D</t>
         </is>
       </c>
-      <c r="O42" s="1" t="inlineStr"/>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L158: isolated marker/symbol line | line starts with punctuation glued to text :: .E</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2869,7 +2877,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L141: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L141: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
